--- a/知体知医_数据模板.xlsx
+++ b/知体知医_数据模板.xlsx
@@ -162,6 +162,246 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>TRAE AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>TRAE AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>TRAE AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>TRAE AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>TRAE AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -448,7 +688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -11754,11 +11994,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -23637,11 +23878,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -28966,11 +29208,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -37018,11 +37261,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -37498,5 +37742,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/知体知医_数据模板.xlsx
+++ b/知体知医_数据模板.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="疾病-测试关联" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="健康调养卡片" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计概览" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问询问题库" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三级测试流程" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -162,246 +164,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>TRAE AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>TRAE AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>TRAE AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>TRAE AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>TRAE AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -688,12 +450,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J217"/>
+  <dimension ref="A1:J218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11992,14 +11754,65 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>🫁</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>幽门螺杆菌感染、胃酸分泌过多、非甾体抗炎药使用、精神压力</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠黏膜被胃酸和胃蛋白酶消化形成溃疡</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>胃镜检查、幽门螺杆菌检测</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>抑酸药物、根除幽门螺杆菌、保护胃黏膜</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>肝胃不和型、脾胃虚弱型、胃阴不足型</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>消化内科</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>urgent</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>胃镜检查, C13/C14呼气试验, 大便潜血试验</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -23878,12 +23691,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -29208,12 +29020,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -37261,12 +37072,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -37433,11 +37243,13 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>消化系统</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>19</v>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>已添加</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -37742,6 +37554,2070 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>疾病名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>问题ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>问题内容</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>选项1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>权重1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>选项2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>权重2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>选项3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>权重3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>q_bp1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常感到头晕、头痛？</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>q_bp2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>您是否有高血压家族史？</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>q_bp3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常心悸、耳鸣？</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>q_bp4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>您的工作是否需要长期久坐？</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>q_bp5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>您是否吸烟或饮酒？</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>q_dm1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>您是否有多饮、多尿、多食症状？</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>q_dm2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>您是否有糖尿病家族史？</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>q_dm3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>您近期是否有不明原因体重下降？</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>q_dm4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常感到口渴？</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>q_dm5</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>您的年龄是否超过45岁？</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>胃炎</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>q_g1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>您是否有胃痛、胃胀症状？</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>胃炎</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>q_g2</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>您是否有反酸、烧心症状？</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>胃炎</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>q_g3</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常饮食不规律？</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>胃炎</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>q_g4</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常吃辛辣刺激食物？</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>胃溃疡</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>q_gu1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>您是否有餐后上腹痛？</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>胃溃疡</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>q_gu2</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>您是否有黑便史？</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>胃溃疡</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>q_gu3</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>您是否服用过非甾体抗炎药？</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>胃溃疡</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>q_gu4</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>您的上腹痛是否有节律性？</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>q_du1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>您是否有空腹痛或夜间痛？</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>q_du2</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>进食后腹痛是否缓解？</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>q_du3</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>您是否有反酸症状？</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>q_du4</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>您是否有黑便史？</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>q_du5</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>您是否长期精神紧张或压力大？</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>q_i1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>您入睡是否需要超过30分钟？</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>q_i2</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>您夜间是否容易醒来？</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>q_i3</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>您是否早醒后难以再入睡？</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>q_i4</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>您白天是否感到困倦乏力？</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>颈椎病</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>q_c1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常颈肩部酸痛？</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>颈椎病</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>q_c2</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>您是否有手麻症状？</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>颈椎病</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>q_c3</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>您是否长期低头工作或使用手机？</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>颈椎病</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>q_c4</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>您是否有头晕症状？</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>冠心病</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>q_chd1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>您是否有胸痛、胸闷症状？</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>冠心病</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>q_chd2</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>您是否有冠心病家族史？</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>冠心病</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>q_chd3</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>您是否有高血压、高血脂或糖尿病？</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>冠心病</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>q_chd4</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>您是否吸烟？</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>焦虑症</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>q_a1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常感到紧张、焦虑？</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>焦虑症</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>q_a2</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>您是否难以控制担忧？</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>焦虑症</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>q_a3</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>您是否有心慌、出汗、手抖等躯体症状？</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>焦虑症</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>q_a4</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>您是否坐立不安？</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>抑郁症</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>q_d1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>您是否对事物失去兴趣？</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>抑郁症</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>q_d2</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>您是否感到情绪低落、沮丧？</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>抑郁症</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>q_d3</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>您是否感到乏力、精力不足？</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>抑郁症</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>q_d4</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>您是否有睡眠问题？</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>痛风</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>q_g1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>您是否有突发关节红肿热痛？</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>痛风</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>q_g2</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>疼痛是否常见于大脚趾？</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>痛风</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>q_g3</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常饮酒或吃海鲜？</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>痛风</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>q_g4</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>您是否有痛风家族史？</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>级别</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>风险权重</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>第1级</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>问询</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>疾病相关症状问询（4-5个问题）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>根据用户回答计算初步风险百分比</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>第2级</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>居家徒手测试</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>自测项目评估（血压、心率等）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>用户可自行完成的简单测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>第3级</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>医院检测</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>专业医疗检测（血液、影像等）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>需在医院进行的专业检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>风险报告</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>综合风险评估报告</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>生成最终风险百分比和就医建议</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/知体知医_数据模板.xlsx
+++ b/知体知医_数据模板.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计概览" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问询问题库" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三级测试流程" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中医运动处方" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推荐食谱" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37563,7 +37565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -39460,6 +39462,1344 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>q_l1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>您是否有腰痛症状？</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>q_l2</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>您是否有腿麻或腿痛症状？</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>q_l3</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>您是否需要久坐工作？</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>q_l4</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>弯腰时腰痛是否加重？</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>q_e1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>您是否有皮肤瘙痒症状？</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>q_e2</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>您是否有皮疹、红斑？</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>q_e3</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>症状是否反复发作？</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>q_e4</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>您是否有过敏史？</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>脂肪肝</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>q_f1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>您是否超重或肥胖？</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>脂肪肝</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>q_f2</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>您是否经常饮酒？</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>脂肪肝</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>q_f3</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>您是否有右上腹不适？</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>脂肪肝</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>q_f4</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>您是否有糖尿病或高血脂？</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>偏头痛</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>q_m1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>您是否有反复发作的头痛？</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>偏头痛</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>q_m2</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>头痛是否为单侧搏动性？</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>偏头痛</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>q_m3</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>头痛时是否有恶心、畏光？</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>偏头痛</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>q_m4</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>头痛持续4-72小时？</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>慢性肾病</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>q_k1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>您是否有泡沫尿？</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>慢性肾病</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>q_k2</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>您是否有水肿（眼睑或下肢）？</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>慢性肾病</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>q_k3</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>您是否有高血压或糖尿病？</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>慢性肾病</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>q_k4</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>您是否有夜尿增多？</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>骨质疏松</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>q_o1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>您是否身高变矮？</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>骨质疏松</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>q_o2</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>您是否有腰背痛？</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>骨质疏松</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>q_o3</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>您是否有过骨折史？</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>骨质疏松</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>q_o4</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>您是否绝经后女性或60岁以上男性？</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>类风湿关节炎</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>q_r1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>您是否有多个关节肿痛？</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>类风湿关节炎</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>q_r2</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>您是否有晨僵（持续&gt;1小时）？</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>类风湿关节炎</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>q_r3</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>症状是否对称出现？</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>类风湿关节炎</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>q_r4</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>症状是否持续超过6周？</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>前列腺增生</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>q_p1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>您是否有尿频、尿急？</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>前列腺增生</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>q_p2</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>您是否有夜尿增多（&gt;2次/夜）？</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>前列腺增生</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>q_p3</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>您是否有排尿困难、尿线变细？</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>前列腺增生</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>q_p4</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>您是否年龄超过50岁？</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>月经失调</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>q_mc1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>您的月经周期是否不规律？</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>月经失调</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>q_mc2</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>您的月经量是否异常？</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>过多</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>过少</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>月经失调</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>q_mc3</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>您是否有痛经？</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>偶尔</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>从不</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>月经失调</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>q_mc4</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>您是否近期压力大或情绪波动？</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -39620,4 +40960,436 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>疾病名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>运动处方（中医具体指导）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>太极拳（每日15-20分钟）、八段锦（每日1-2遍）、涌泉穴按摩（每侧3分钟）、深呼吸法（每日3次×5分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>八段锦"调理脾胃须单举"（每日10次）、太极拳（每日15-20分钟）、耳部按摩（每日3次×2分钟）、转腰运动（每日2次×20圈）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>安神功（盘坐闭目意守丹田15-20分钟）、搓涌泉穴（每侧100次）、叩齿吞津（每日36次）、八段锦"两手攀足固肾腰"（每日10次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>颈椎病</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>颈椎操（米字操各方向5次+颈部对抗10次）、八段锦"五劳七伤往后瞧"（每日10次）、大鹏展翅（每日10次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>五禽戏"鹿戏"（每日10-15分钟）、八段锦"两手攀足固肾腰"（每日10次）、飞燕式（每日10次）、拱桥式（每日10次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>胃炎</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>八段锦"调理脾胃须单举"（每日10次）、腹部按摩（顺逆各36圈）、足三里穴按摩（每侧3分钟）、呼吸吐纳（每日10分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>腹部按摩（上腹部顺时针36圈）、足三里穴按摩（每侧3分钟）、内关穴按摩（每侧2分钟）、八段锦"调理脾胃须单举"（每日10次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>冠心病</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>太极拳（每日15-20分钟）、八段锦"左右开弓似射雕"（每日10次）、内关穴按摩（每侧3分钟）、散步（餐后30分钟×20-30分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>焦虑症</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>六字诀"呵"字功（每日6-12次）、八段锦"摇头摆尾去心火"（每日10次）、太极拳（每日15-20分钟）、腹式呼吸（每日10分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>抑郁症</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>八段锦全套（每日1-2遍）、太极拳（每日15-20分钟）、晒太阳（上午9-10点×20分钟）、散步（每日30分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>痛风</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>太极拳（每日15-20分钟）、关节活动操（趾关节+踝关节各方向活动，每日2次）、多饮水（每日2000ml以上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>偏头痛</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>风池穴按摩（每侧3分钟）、合谷穴按摩（每侧2分钟）、八段锦"五劳七伤往后瞧"（每日10次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>贫血</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>八段锦全套（每日1-2遍）、足三里穴按摩（每侧3分钟）、三阴交穴按摩（每侧3分钟）、散步（每日30分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>甲状腺功能亢进</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>太极拳（每日15-20分钟，动作柔和）、八段锦"两手攀足固肾腰"（每日10次）、腹式呼吸（每日10分钟）、避免剧烈运动</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>甲状腺功能减退</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>八段锦全套（每日1-2遍）、足三里穴按摩（每侧3分钟）、关元穴按摩（3分钟）、晒太阳（上午20分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>类风湿关节炎</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>太极拳（每日15-20分钟）、关节活动操（各方向5-10次，每日2次）、八段锦"左右开弓似射雕"（每日10次）、运动前热敷15分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>骨质疏松</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>八段锦"两手攀足固肾腰"（每日10次）、太极拳（每日15-20分钟）、踮脚运动（30秒×10次）、散步+晒太阳（每日30分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>过敏性鼻炎</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>迎香穴按摩（每侧2分钟）、八段锦"左右开弓似射雕"（每日10次）、搓鼻法（每日3次×36次）、腹式呼吸（每日10分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>哮喘</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>六字诀"呬"字功（每日6-12次）、八段锦"左右开弓似射雕"（每日10次）、腹式呼吸（每日10-15分钟）、太极拳（每日15-20分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>脂肪肝</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>八段锦全套（每日1-2遍）、仰卧起坐（每日3组×15-20个）、足三里穴按摩（每侧3分钟）、快走（每日30-40分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>慢性肾病</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>八段锦"两手攀足固肾腰"（每日10次）、太极拳（每日15-20分钟）、涌泉穴按摩（每侧100次）、避免剧烈运动</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>八段锦全套（每日1遍）、散步（每日30分钟）、避免剧烈运动和过度出汗、保持皮肤清洁干燥</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>前列腺增生</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>提肛运动（每日3次×30次）、八段锦"两手攀足固肾腰"（每日10次）、涌泉穴按摩（每侧100次）、避免久坐</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>月经失调</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>八段锦全套（每日1-2遍）、三阴交穴按摩（每侧3分钟）、关元穴按摩（3分钟）、太极拳（每日15-20分钟）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>疾病名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>推荐食谱</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>芹菜炒百合（芹菜200g+百合50g清炒）、山楂决明子茶（山楂10g+决明子10g开水冲泡代茶饮）、凉拌黑木耳（黑木耳100g+洋葱50g+少许醋凉拌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>苦瓜炒鸡蛋（苦瓜200g+鸡蛋1个少油清炒）、山药薏仁粥（山药50g+薏仁30g+大米50g煮粥）、凉拌黄瓜（黄瓜200g+蒜末+少许醋凉拌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>胃炎</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>小米南瓜粥（小米50g+南瓜100g煮粥养胃）、山药莲子粥（山药50g+莲子20g+大米50g健脾养胃）、猴头菇炖鸡汤（猴头菇50g+鸡肉200g小火炖2小时）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>山药莲子粥（山药50g+莲子20g+大米50g健脾护胃）、猴头菇炖鸡汤（猴头菇50g+鸡肉200g小火炖2小时促进溃疡愈合）、蜂蜜水（温水冲服蜂蜜1勺晨起空腹饮用保护胃黏膜）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>酸枣仁粥（酸枣仁30g+大米50g煮粥安神助眠）、百合莲子羹（百合30g+莲子20g+冰糖适量炖煮）、桂圆红枣茶（桂圆5个+红枣3个开水冲泡睡前1小时饮用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>冠心病</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>山楂粥（山楂30g+大米50g煮粥活血化瘀）、黑木耳炒芹菜（黑木耳100g+芹菜200g清炒）、三七粉冲服（三七粉3g+温水冲服每日1次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>贫血</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>红枣桂圆粥（红枣10个+桂圆肉30g+大米50g煮粥）、菠菜猪肝汤（菠菜200g+猪肝100g煮汤）、当归羊肉汤（当归10g+羊肉200g炖煮2小时）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/知体知医_数据模板.xlsx
+++ b/知体知医_数据模板.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三级测试流程" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中医运动处方" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推荐食谱" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="症状-疾病映射" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +43,33 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +79,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="003ABFA8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +138,33 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11813,6 +11886,1227 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>疾病名称</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>症状关键词（逗号分隔）</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>关键词数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>头晕,头痛,血压高,血压,头昏,眩晕,心悸,耳鸣,后脑痛,视物模糊</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>多饮,多尿,多食,血糖,口渴,消瘦,尿频,皮肤瘙痒,伤口不愈,手脚麻木</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>胃炎</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>胃痛,胃胀,反酸,烧心,胃不适,恶心,胃酸,上腹痛,饭后胀,嗳气,食欲不振,肚子疼,腹痛</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>十二指肠溃疡</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>空腹痛,夜间痛,饥饿痛,反酸,黑便,十二指肠,肚子疼,腹痛,饭后痛</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>肠炎</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>腹泻,拉肚子,腹痛,肚子疼,腹胀,大便次数多,黏液便,里急后重,肠鸣</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>胃溃疡</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>胃痛,饭后痛,反酸,黑便,呕血,上腹痛,肚子疼,腹痛,体重下降</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>消化不良</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>胃胀,腹胀,早饱,嗳气,恶心,食欲不振,肚子疼,上腹不适</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>胆囊炎</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>右上腹痛,发热,恶心,黄疸,胆囊,油腻,肚子疼,腹痛,后背痛</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>肝硬化</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>腹胀,腹水,黄疸,乏力,食欲差,蜘蛛痣,肝掌,鼻子出血</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>脂肪肝</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>肝区不适,脂肪肝,转氨酶,右上腹,乏力,腹胀</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>阑尾炎</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>右下腹痛,转移性腹痛,发热,恶心,呕吐,肚子疼,腹痛,麦氏点</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>肠易激综合征</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>腹痛,腹泻,便秘,肚子疼,腹胀,排便习惯改变,黏液便,情绪紧张</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>便秘</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>便秘,排便困难,大便干,几天不排便,腹胀,用力排便</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>睡不着,失眠,入睡困难,早醒,睡眠差,多梦,睡眠,整夜不眠</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>焦虑症</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>焦虑,紧张,担心,坐立不安,心慌,恐慌,胸闷,手心出汗,呼吸急促</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>抑郁症</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>抑郁,情绪低落,兴趣减退,乏力,消极,绝望,失眠,食欲下降,自责</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>颈椎病</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>颈痛,脖子痛,肩颈,手麻,脖子硬,颈椎,头晕,手指麻木,肩痛</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>腰痛,腿麻,腰酸,坐骨神经,腰椎,腰腿,下肢放射痛,弯腰困难</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>偏头痛</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>偏头痛,搏动性头痛,一侧头痛,恶心,畏光,视觉先兆</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>紧张性头痛</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>头痛,头部紧压感,两侧头痛,肩颈痛,紧张,压力</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>痛风</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>关节痛,脚趾痛,红肿热痛,尿酸,痛风,大脚趾,夜间痛</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>类风湿关节炎</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>关节肿痛,晨僵,关节变形,类风湿,对称性关节痛,手指关节</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>骨关节炎</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>关节痛,上下楼梯痛,膝关节痛,关节僵硬,活动后加重,老年人</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>骨质疏松</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>骨痛,腰背痛,身高变矮,骨折,骨密度,驼背</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>冠心病</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>胸痛,胸闷,心绞痛,心前区,胸闷气短,活动后胸闷,心慌</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>心律失常</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>心悸,心跳不齐,心慌,心跳快,心跳慢,漏跳,胸闷</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>心力衰竭</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>呼吸困难,下肢水肿,乏力,夜间憋醒,端坐呼吸,心慌,胸闷</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>心肌炎</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>胸闷,心悸,乏力,发热,气短,心跳快,感冒后心慌</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>肺炎</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>发热,咳嗽,咳痰,胸痛,气促,高热,寒战,呼吸困难</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>支气管炎</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>咳嗽,咳痰,气喘,慢性咳嗽,白色泡沫痰,反复咳嗽</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>哮喘</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>喘息,气短,呼吸困难,哮鸣,夜间喘息,咳嗽变异性</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>过敏性鼻炎</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>打喷嚏,流鼻涕,鼻塞,鼻痒,鼻子痒,季节性</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>慢性阻塞性肺疾病</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>咳嗽,气短,呼吸困难,慢性咳嗽,吸烟,活动后气促</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>贫血</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>面色苍白,心悸,气短,贫血,头晕,乏力,指甲苍白,蹲起头晕</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>甲状腺功能亢进</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>心慌,手抖,消瘦,怕热,多汗,突眼,甲亢,大便次数多,脾气急</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>甲状腺功能减退</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>乏力,怕冷,浮肿,便秘,体重增加,甲减,记忆力差,皮肤干燥</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>皮肤痒,皮疹,湿疹,皮肤红,瘙痒,渗出,反复发作</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>荨麻疹</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>风团,皮肤痒,荨麻疹,红色肿块,反复发作,过敏</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>银屑病</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>皮疹,银白色鳞屑,关节痛,指甲改变,银屑病,牛皮癣,反复发作</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>带状疱疹</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>水疱,疼痛,皮疹,带状,神经痛,单侧分布</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>慢性肾病</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>泡沫尿,水肿,尿少,腰酸,肾功能,乏力,食欲差,贫血</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>尿路感染</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>尿频,尿急,尿痛,发热,腰痛,血尿,下腹痛</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>前列腺增生</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>尿频,尿急,排尿困难,夜尿多,尿不尽,老年人</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>肾结石</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>腰痛,血尿,腹痛,尿频,恶心,呕吐,剧烈腰痛</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>痛经</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>痛经,月经痛,经期腹痛,下腹痛,月经期</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>月经失调</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>月经不调,月经紊乱,经期不规律,月经量多,月经量少</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>多囊卵巢综合征</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>月经不调,多毛,肥胖,不孕,痤疮,月经紊乱</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>子宫肌瘤</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>月经量多,腹痛,腹部包块,尿频,便秘,经期延长</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>脑卒中</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>偏瘫,口角歪斜,言语不清,头痛,头晕,突然无力,肢体麻木</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>帕金森病</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>手抖,动作慢,僵硬,步态异常,震颤,面具脸,小碎步</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>阿尔茨海默病</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>记忆力下降,遗忘,定向障碍,认知下降,老年痴呆,迷路</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>干眼症</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>眼干,眼涩,异物感,视疲劳,眼睛干,畏光</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>青光眼</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>眼痛,头痛,视力下降,虹视,眼压高,恶心,视野缺损</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>视力下降,视物模糊,眩光,老年人,无痛性视力下降</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>中耳炎</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>耳痛,听力下降,耳流脓,发热,耳朵闷</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>扁桃体炎</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>咽痛,发热,吞咽困难,扁桃体肿大,喉咙痛</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>胃食管反流病</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>反酸,烧心,胸骨后灼热,夜间咳嗽,嗓子异物感,嗳气</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>功能性消化不良</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>上腹不适,早饱,腹胀,恶心,嗳气,无器质性病变</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>缺铁性贫血</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>面色苍白,乏力,头晕,心悸,指甲变薄,异食癖</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>巨幼细胞贫血</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>乏力,头晕,舌炎,手脚麻木,食欲不振,腹泻</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>过敏性紫癜</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>皮肤紫癜,关节痛,腹痛,血尿,下肢出血点</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>系统性红斑狼疮</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>面部红斑,关节痛,发热,光过敏,口腔溃疡,脱发</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>干燥综合征</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>口干,眼干,关节痛,反复腮腺肿大,皮肤干燥</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>强直性脊柱炎</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>腰背痛,晨僵,脊柱僵硬,髋关节痛,年轻男性,夜间痛</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>肩周炎</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>肩痛,肩关节活动受限,抬臂困难,夜间痛,肩膀僵硬</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>网球肘</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>肘痛,握物无力,前臂疼痛,拧毛巾痛</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>坐骨神经痛</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>腰腿痛,臀部放射痛,下肢麻木,直腿抬高痛,坐骨神经</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>植物神经功能紊乱</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>心慌,出汗,失眠,头晕,腹胀,焦虑,多系统症状</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>慢性胃炎</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>胃痛,胃胀,反酸,嗳气,食欲不振,上腹不适,肚子疼</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>急性胃肠炎</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>腹泻,呕吐,腹痛,发热,恶心,肚子疼,水样便</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>痔疮</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>便血,肛门痛,肛门肿物,便秘,排便时出血</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>肝功能异常</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>乏力,食欲差,黄疸,肝区不适,转氨酶升高,恶心</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>高脂血症</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>头晕,乏力,黄色瘤,肥胖,血脂高,脂肪肝</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>高尿酸血症</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>关节痛,尿酸高,痛风,脚趾痛,红肿</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>维生素D缺乏</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>骨痛,肌肉无力,骨折,乏力,骨质疏松</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>睡眠呼吸暂停综合征</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>打鼾,白天嗜睡,夜间憋醒,晨起头痛,肥胖</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>慢性疲劳综合征</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>持续疲劳,休息后不缓解,肌肉痛,记忆力差,睡眠后仍疲劳</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>更年期综合征</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>潮热,盗汗,情绪波动,月经紊乱,失眠,心慌</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>前列腺炎</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>尿频,尿急,下腹痛,会阴不适,腰骶痛,排尿不适</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -37083,7 +38377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37552,6 +38846,47 @@
       </c>
       <c r="E36" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>症状-疾病映射统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>映射疾病数量</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>风险过滤阈值</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>反馈&lt;5%不显示，测试&lt;20%自动清除</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>合规声明</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>已添加</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -40812,7 +42147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -40957,7 +42292,41 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>低风险自动清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>反馈识别&lt;5%不显示，测试结果&lt;20%自动从风险中移除</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>合规免责声明</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>所有风险提示页面均显示"仅进行风险提示，不作为疾病诊断依据"</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/知体知医_数据模板.xlsx
+++ b/知体知医_数据模板.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中医运动处方" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推荐食谱" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="症状-疾病映射" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科室分类" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13177,6 +13178,339 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>大类</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>对应科室</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>显示所有疾病</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>心血管</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>心内科,心外科,血管外科,心脏外科,CCU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>高血压、冠心病、心律失常等</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>消化</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>消化内科,肝病科,肝胆外科,肛肠外科,胃肠外科</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>胃炎、胃溃疡、脂肪肝等</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>呼吸</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>呼吸内科,胸外科,感染科</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>肺炎、哮喘、慢阻肺等</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>内分泌</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>内分泌科,营养科,甲状腺外科,烧伤科</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>糖尿病、甲状腺疾病、痛风等</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>神经</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>神经内科,神经外科,睡眠医学科</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>脑卒中、帕金森、失眠等</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>精神心理</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>精神科,心理科,心身医学科</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>焦虑症、抑郁症等</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>骨科</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>骨科,康复科,关节外科,脊柱外科,手外科,运动医学科</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>骨质疏松、颈椎病等</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>泌尿</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>泌尿外科,肾内科</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>肾结石、慢性肾病等</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>妇科</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>妇科,生殖医学科,乳腺外科</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>月经不调、乳腺疾病等</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>皮肤</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>皮肤科,整形外科</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>湿疹、荨麻疹等</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>风湿免疫</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>风湿免疫科</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>类风湿、红斑狼疮等</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>耳鼻喉</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>耳鼻喉科,变态反应科</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>过敏性鼻炎等</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>青光眼、白内障等</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>血液科</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>贫血、白血病等</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>儿科</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>儿科,儿童心理科</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>儿童常见疾病</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>肿瘤</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>肿瘤科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>各类肿瘤</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>普外</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>普外科,急诊科</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>急腹症、外伤等</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -38988,6 +39322,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
@@ -39800,8 +40135,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -39835,8 +40168,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
